--- a/share_dinkum_proj/share_dinkum_app/import_data/data_import_template_public.xlsx
+++ b/share_dinkum_proj/share_dinkum_app/import_data/data_import_template_public.xlsx
@@ -636,7 +636,7 @@
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>Which line of the statement this is.
-One of: DISCOUNTED_TAP (Discounted capital gains - taxable Australian property); DISCOUNTED_NTAP (Discounted capital gains - non-taxable Australian property); OTHER_TAP (Other method capital gains - taxable Australian property); OTHER_NTAP (Other method capital gains - non-taxable Australian property); FOREIGN_CG_DISCOUNTED (Taxable foreign capital gains - discounted method); FOREIGN_CG_OTHER (Taxable foreign capital gains - other method); AMIT_GROSS_UP (AMIT CGT gross up amount); NET_CAPITAL_GAIN (Net capital gain); TOTAL_CY_CG (Total current year capital gains); OTHER_CG_DISTRIBUTION (Other capital gains distribution); COSTBASE_INCREASE (AMIT cost base net amount - shortfall (increase cost base)); COSTBASE_DECREASE (AMIT cost base net amount - excess (reduce cost base)); and 14 more.
+One of: DISCOUNTED_TAP (Discounted capital gains - taxable Australian property); DISCOUNTED_NTAP (Discounted capital gains - non-taxable Australian property); OTHER_TAP (Other method capital gains - taxable Australian property); OTHER_NTAP (Other method capital gains - non-taxable Australian property); FOREIGN_CG_DISCOUNTED (Taxable foreign capital gains - discounted method); FOREIGN_CG_OTHER (Taxable foreign capital gains - other method); AMIT_GROSS_UP (AMIT CGT gross up amount); NET_CAPITAL_GAIN (Net capital gain); TOTAL_CY_CG (Total current year capital gains); OTHER_CG_DISTRIBUTION (Other capital gains distribution); COSTBASE_INCREASE (AMIT cost base net amount - shortfall (increase cost base)); COSTBASE_DECREASE (AMIT cost base net amount - excess (reduce cost base)); and 15 more.
 Required.</t>
       </text>
     </comment>
@@ -1264,8 +1264,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="AttributionComponent" displayName="AttributionComponent" ref="A1:G219" headerRowCount="1">
-  <autoFilter ref="A1:G219"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="AttributionComponent" displayName="AttributionComponent" ref="A1:G231" headerRowCount="1">
+  <autoFilter ref="A1:G231"/>
   <tableColumns count="7">
     <tableColumn id="1" name="legacy_id"/>
     <tableColumn id="2" name="description"/>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="E15" s="2">
         <f>HYPERLINK("#'14'!A1", "14")</f>
@@ -14331,7 +14331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G219"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.2" customWidth="1" min="1" max="1"/>
@@ -14392,7 +14392,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.04</v>
+        <v>4.45</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.04</v>
+        <v>4.45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.55</v>
+        <v>11.04</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>93.45999999999999</v>
+        <v>136.77</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.58</v>
+        <v>22.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.390000000000001</v>
+        <v>12.27</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.4</v>
+        <v>3.51</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -14588,16 +14588,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AS001-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS001-FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.84</v>
+        <v>58.62</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -14613,16 +14613,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AS001-COSTBASE_INCREASE</t>
+          <t>AS001-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.7</v>
+        <v>1.23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -14638,16 +14638,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AS002-DISCOUNTED_NTAP</t>
+          <t>AS001-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.16</v>
+        <v>2.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -14656,23 +14656,23 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS002</t>
+          <t>AS001</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AS002-OTHER_NTAP</t>
+          <t>AS002-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.11</v>
+        <v>6.16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -14688,16 +14688,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AS002-AMIT_GROSS_UP</t>
+          <t>AS002-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6.16</v>
+        <v>2.11</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -14713,16 +14713,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AS002-TOTAL_CY_CG</t>
+          <t>AS002-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.43</v>
+        <v>6.16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -14738,16 +14738,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AS002-FOREIGN_SOURCE_INCOME</t>
+          <t>AS002-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>74.41</v>
+        <v>14.43</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -14763,16 +14763,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AS002-INTEREST</t>
+          <t>AS002-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.96</v>
+        <v>74.41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -14788,16 +14788,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AS002-UNFRANKED_DISTRIBUTION</t>
+          <t>AS002-INTEREST</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.79</v>
+        <v>3.96</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -14813,16 +14813,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AS002-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS002-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7.44</v>
+        <v>0.79</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -14838,16 +14838,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AS002-COSTBASE_INCREASE</t>
+          <t>AS002-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7.49</v>
+        <v>7.44</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -14863,16 +14863,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AS003-DISCOUNTED_NTAP</t>
+          <t>AS002-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>32.76</v>
+        <v>7.49</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -14881,23 +14881,23 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AS003</t>
+          <t>AS002</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AS003-OTHER_NTAP</t>
+          <t>AS003-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.07</v>
+        <v>46.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -14913,16 +14913,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AS003-AMIT_GROSS_UP</t>
+          <t>AS003-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>32.76</v>
+        <v>2.95</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -14938,16 +14938,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AS003-TOTAL_CY_CG</t>
+          <t>AS003-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>67.59</v>
+        <v>46.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -14963,16 +14963,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AS003-FRANKED_DISTRIBUTION</t>
+          <t>AS003-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FRANKED_DISTRIBUTION</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>397.97</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -14988,16 +14988,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AS003-UNFRANKED_DISTRIBUTION</t>
+          <t>AS003-FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>66.33</v>
+        <v>566.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -15013,16 +15013,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AS003-FOREIGN_SOURCE_INCOME</t>
+          <t>AS003-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>35.71</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -15038,16 +15038,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AS003-INTEREST</t>
+          <t>AS003-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.2</v>
+        <v>50.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -15063,16 +15063,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AS003-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS003-INTEREST</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3.57</v>
+        <v>14.52</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -15088,16 +15088,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AS003-COSTBASE_DECREASE</t>
+          <t>AS003-FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>COSTBASE_DECREASE</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>67.83</v>
+        <v>242.61</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -15113,16 +15113,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AS004-DISCOUNTED_NTAP</t>
+          <t>AS003-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21.2</v>
+        <v>5.08</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -15131,23 +15131,23 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AS004</t>
+          <t>AS003</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AS004-OTHER_NTAP</t>
+          <t>AS003-COSTBASE_DECREASE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>COSTBASE_DECREASE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7.1</v>
+        <v>67.83</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -15156,19 +15156,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AS004</t>
+          <t>AS003</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AS004-AMIT_GROSS_UP</t>
+          <t>AS004-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -15188,16 +15188,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AS004-TOTAL_CY_CG</t>
+          <t>AS004-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>49.5</v>
+        <v>7.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -15213,16 +15213,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AS004-FOREIGN_SOURCE_INCOME</t>
+          <t>AS004-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>426.37</v>
+        <v>21.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -15238,16 +15238,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AS004-INTEREST</t>
+          <t>AS004-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>22.68</v>
+        <v>49.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -15263,16 +15263,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AS004-UNFRANKED_DISTRIBUTION</t>
+          <t>AS004-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4.54</v>
+        <v>426.37</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -15288,16 +15288,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AS004-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS004-INTEREST</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>42.64</v>
+        <v>22.68</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -15313,16 +15313,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AS004-COSTBASE_DECREASE</t>
+          <t>AS004-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>COSTBASE_DECREASE</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>60.31</v>
+        <v>4.54</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -15338,16 +15338,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AS005-DISCOUNTED_TAP</t>
+          <t>AS004-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DISCOUNTED_TAP</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.79</v>
+        <v>42.64</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -15356,23 +15356,23 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AS005</t>
+          <t>AS004</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AS005-DISCOUNTED_NTAP</t>
+          <t>AS004-COSTBASE_DECREASE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>COSTBASE_DECREASE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.24</v>
+        <v>60.31</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -15381,23 +15381,23 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AS005</t>
+          <t>AS004</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AS005-OTHER_NTAP</t>
+          <t>AS005-DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -15413,16 +15413,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AS005-AMIT_GROSS_UP</t>
+          <t>AS005-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.03</v>
+        <v>14.86</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -15438,16 +15438,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AS005-TOTAL_CY_CG</t>
+          <t>AS005-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>23.16</v>
+        <v>1.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -15463,16 +15463,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AS005-FRANKED_DISTRIBUTION</t>
+          <t>AS005-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FRANKED_DISTRIBUTION</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>169.63</v>
+        <v>16.01</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -15488,16 +15488,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AS005-UNFRANKED_DISTRIBUTION</t>
+          <t>AS005-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25.44</v>
+        <v>33.62</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -15513,16 +15513,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AS005-FOREIGN_SOURCE_INCOME</t>
+          <t>AS005-FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.72</v>
+        <v>246.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -15538,16 +15538,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AS005-INTEREST</t>
+          <t>AS005-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4.24</v>
+        <v>36.91</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -15563,16 +15563,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AS005-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS005-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1.27</v>
+        <v>18.46</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -15588,16 +15588,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AS005-COSTBASE_INCREASE</t>
+          <t>AS005-INTEREST</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.66</v>
+        <v>6.15</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -15613,16 +15613,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AS006-DISCOUNTED_NTAP</t>
+          <t>AS005-FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>30.95</v>
+        <v>105.47</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -15631,23 +15631,23 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AS006</t>
+          <t>AS005</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AS006-OTHER_NTAP</t>
+          <t>AS005-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -15656,23 +15656,23 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AS006</t>
+          <t>AS005</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AS006-AMIT_GROSS_UP</t>
+          <t>AS005-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>30.95</v>
+        <v>14.66</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -15681,23 +15681,23 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AS006</t>
+          <t>AS005</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AS006-TOTAL_CY_CG</t>
+          <t>AS006-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>65.15000000000001</v>
+        <v>45.31</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -15713,16 +15713,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AS006-FRANKED_DISTRIBUTION</t>
+          <t>AS006-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FRANKED_DISTRIBUTION</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>821.49</v>
+        <v>4.75</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -15738,16 +15738,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AS006-UNFRANKED_DISTRIBUTION</t>
+          <t>AS006-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>136.92</v>
+        <v>45.31</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -15763,16 +15763,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AS006-FOREIGN_SOURCE_INCOME</t>
+          <t>AS006-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>73.72</v>
+        <v>95.37</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -15788,16 +15788,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AS006-INTEREST</t>
+          <t>AS006-FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>21.06</v>
+        <v>1202.59</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -15813,16 +15813,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AS006-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS006-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>7.37</v>
+        <v>200.43</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -15838,16 +15838,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AS006-COSTBASE_INCREASE</t>
+          <t>AS006-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>54.17</v>
+        <v>107.93</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -15863,16 +15863,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AS007-DISCOUNTED_NTAP</t>
+          <t>AS006-INTEREST</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>59.11</v>
+        <v>30.84</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -15881,23 +15881,23 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AS007</t>
+          <t>AS006</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AS007-OTHER_NTAP</t>
+          <t>AS006-FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2.75</v>
+        <v>515.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -15906,23 +15906,23 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AS007</t>
+          <t>AS006</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AS007-AMIT_GROSS_UP</t>
+          <t>AS006-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>59.11</v>
+        <v>10.79</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -15931,23 +15931,23 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AS007</t>
+          <t>AS006</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AS007-TOTAL_CY_CG</t>
+          <t>AS006-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>120.97</v>
+        <v>54.17</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -15956,23 +15956,23 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AS007</t>
+          <t>AS006</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AS007-FOREIGN_SOURCE_INCOME</t>
+          <t>AS007-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1182.6</v>
+        <v>59.11</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -15988,16 +15988,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AS007-INTEREST</t>
+          <t>AS007-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>62.9</v>
+        <v>2.75</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -16013,16 +16013,16 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AS007-UNFRANKED_DISTRIBUTION</t>
+          <t>AS007-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.58</v>
+        <v>59.11</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -16038,16 +16038,16 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AS007-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS007-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>118.26</v>
+        <v>120.97</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -16063,16 +16063,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AS007-COSTBASE_INCREASE</t>
+          <t>AS007-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>46.66</v>
+        <v>1182.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -16088,16 +16088,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AS008-DISCOUNTED_TAP</t>
+          <t>AS007-INTEREST</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DISCOUNTED_TAP</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2.42</v>
+        <v>62.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -16106,23 +16106,23 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AS008</t>
+          <t>AS007</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AS008-DISCOUNTED_NTAP</t>
+          <t>AS007-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>46.09</v>
+        <v>12.58</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -16131,23 +16131,23 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AS008</t>
+          <t>AS007</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AS008-OTHER_NTAP</t>
+          <t>AS007-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.5</v>
+        <v>118.26</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -16156,23 +16156,23 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AS008</t>
+          <t>AS007</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AS008-AMIT_GROSS_UP</t>
+          <t>AS007-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>48.51</v>
+        <v>46.66</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -16181,23 +16181,23 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AS008</t>
+          <t>AS007</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AS008-TOTAL_CY_CG</t>
+          <t>AS008-DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>108.52</v>
+        <v>3.47</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -16213,16 +16213,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AS008-FRANKED_DISTRIBUTION</t>
+          <t>AS008-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FRANKED_DISTRIBUTION</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>600.49</v>
+        <v>65.95</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -16238,16 +16238,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AS008-UNFRANKED_DISTRIBUTION</t>
+          <t>AS008-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>90.06999999999999</v>
+        <v>16.46</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -16263,16 +16263,16 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AS008-FOREIGN_SOURCE_INCOME</t>
+          <t>AS008-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>45.04</v>
+        <v>69.42</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -16288,16 +16288,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AS008-INTEREST</t>
+          <t>AS008-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>15.01</v>
+        <v>155.3</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -16313,16 +16313,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AS008-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS008-FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>4.5</v>
+        <v>859.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -16338,16 +16338,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AS008-COSTBASE_INCREASE</t>
+          <t>AS008-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>54.14</v>
+        <v>128.88</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -16363,16 +16363,16 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AS009-DISCOUNTED_NTAP</t>
+          <t>AS008-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>9.69</v>
+        <v>64.44</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -16381,23 +16381,23 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AS009</t>
+          <t>AS008</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AS009-OTHER_NTAP</t>
+          <t>AS008-INTEREST</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2.29</v>
+        <v>21.48</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -16406,23 +16406,23 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AS009</t>
+          <t>AS008</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AS009-AMIT_GROSS_UP</t>
+          <t>AS008-FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>9.69</v>
+        <v>368.23</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -16431,23 +16431,23 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AS009</t>
+          <t>AS008</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AS009-TOTAL_CY_CG</t>
+          <t>AS008-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21.67</v>
+        <v>6.44</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -16456,23 +16456,23 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AS009</t>
+          <t>AS008</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AS009-FRANKED_DISTRIBUTION</t>
+          <t>AS008-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FRANKED_DISTRIBUTION</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>69.27</v>
+        <v>54.14</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -16481,23 +16481,23 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AS009</t>
+          <t>AS008</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AS009-UNFRANKED_DISTRIBUTION</t>
+          <t>AS009-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.55</v>
+        <v>13.27</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -16513,16 +16513,16 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AS009-FOREIGN_SOURCE_INCOME</t>
+          <t>AS009-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6.22</v>
+        <v>3.14</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -16538,16 +16538,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AS009-INTEREST</t>
+          <t>AS009-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1.78</v>
+        <v>13.27</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -16563,16 +16563,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AS009-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS009-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.62</v>
+        <v>29.68</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -16588,16 +16588,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AS009-COSTBASE_INCREASE</t>
+          <t>AS009-FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>4.41</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -16613,16 +16613,16 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AS010-DISCOUNTED_NTAP</t>
+          <t>AS009-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>92.23</v>
+        <v>15.82</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -16631,23 +16631,23 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AS010</t>
+          <t>AS009</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AS010-OTHER_NTAP</t>
+          <t>AS009-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>38.35</v>
+        <v>8.52</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -16656,23 +16656,23 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AS010</t>
+          <t>AS009</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AS010-AMIT_GROSS_UP</t>
+          <t>AS009-INTEREST</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>92.23</v>
+        <v>2.43</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -16681,23 +16681,23 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AS010</t>
+          <t>AS009</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AS010-TOTAL_CY_CG</t>
+          <t>AS009-FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>222.81</v>
+        <v>40.69</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -16706,23 +16706,23 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AS010</t>
+          <t>AS009</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AS010-FOREIGN_SOURCE_INCOME</t>
+          <t>AS009-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1713.15</v>
+        <v>0.85</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -16731,23 +16731,23 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AS010</t>
+          <t>AS009</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AS010-INTEREST</t>
+          <t>AS009-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>91.12</v>
+        <v>4.41</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -16756,23 +16756,23 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AS010</t>
+          <t>AS009</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AS010-UNFRANKED_DISTRIBUTION</t>
+          <t>AS010-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>18.22</v>
+        <v>92.23</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -16788,16 +16788,16 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AS010-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS010-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>171.31</v>
+        <v>38.35</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -16813,16 +16813,16 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AS010-COSTBASE_INCREASE</t>
+          <t>AS010-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>167.97</v>
+        <v>92.23</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -16838,16 +16838,16 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AS011-DISCOUNTED_TAP</t>
+          <t>AS010-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DISCOUNTED_TAP</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>4.64</v>
+        <v>222.81</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -16856,23 +16856,23 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>AS011</t>
+          <t>AS010</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AS011-DISCOUNTED_NTAP</t>
+          <t>AS010-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>80.01000000000001</v>
+        <v>1713.15</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -16881,23 +16881,23 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AS011</t>
+          <t>AS010</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AS011-OTHER_NTAP</t>
+          <t>AS010-INTEREST</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>35.35</v>
+        <v>91.12</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -16906,23 +16906,23 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AS011</t>
+          <t>AS010</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AS011-AMIT_GROSS_UP</t>
+          <t>AS010-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>84.65000000000001</v>
+        <v>18.22</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -16931,23 +16931,23 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AS011</t>
+          <t>AS010</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AS011-TOTAL_CY_CG</t>
+          <t>AS010-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>204.65</v>
+        <v>171.31</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -16956,23 +16956,23 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AS011</t>
+          <t>AS010</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AS011-FRANKED_DISTRIBUTION</t>
+          <t>AS010-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FRANKED_DISTRIBUTION</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>641.23</v>
+        <v>167.97</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -16981,23 +16981,23 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AS011</t>
+          <t>AS010</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AS011-UNFRANKED_DISTRIBUTION</t>
+          <t>AS011-DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>96.18000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -17013,16 +17013,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AS011-FOREIGN_SOURCE_INCOME</t>
+          <t>AS011-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>48.09</v>
+        <v>110.27</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -17038,16 +17038,16 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AS011-INTEREST</t>
+          <t>AS011-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>16.03</v>
+        <v>48.72</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -17063,16 +17063,16 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AS011-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS011-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4.81</v>
+        <v>116.67</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -17088,16 +17088,16 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AS011-COSTBASE_INCREASE</t>
+          <t>AS011-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>48.94</v>
+        <v>282.06</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -17113,16 +17113,16 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AS012-DISCOUNTED_NTAP</t>
+          <t>AS011-FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>222.53</v>
+        <v>883.76</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -17131,23 +17131,23 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AS012</t>
+          <t>AS011</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AS012-OTHER_NTAP</t>
+          <t>AS011-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>15.32</v>
+        <v>132.56</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -17156,23 +17156,23 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AS012</t>
+          <t>AS011</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AS012-AMIT_GROSS_UP</t>
+          <t>AS011-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>222.53</v>
+        <v>66.28</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -17181,23 +17181,23 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AS012</t>
+          <t>AS011</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AS012-TOTAL_CY_CG</t>
+          <t>AS011-INTEREST</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>460.38</v>
+        <v>22.09</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -17206,23 +17206,23 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AS012</t>
+          <t>AS011</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AS012-FOREIGN_SOURCE_INCOME</t>
+          <t>AS011-FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1499.98</v>
+        <v>378.75</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -17231,23 +17231,23 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>AS012</t>
+          <t>AS011</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AS012-INTEREST</t>
+          <t>AS011-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>79.79000000000001</v>
+        <v>6.63</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -17256,23 +17256,23 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>AS012</t>
+          <t>AS011</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AS012-UNFRANKED_DISTRIBUTION</t>
+          <t>AS011-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>15.96</v>
+        <v>48.94</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -17281,23 +17281,23 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AS012</t>
+          <t>AS011</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AS012-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS012-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>150</v>
+        <v>222.53</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -17313,16 +17313,16 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AS012-COSTBASE_INCREASE</t>
+          <t>AS012-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>99.95999999999999</v>
+        <v>15.32</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -17338,16 +17338,16 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AS013-DISCOUNTED_TAP</t>
+          <t>AS012-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>DISCOUNTED_TAP</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>8.220000000000001</v>
+        <v>222.53</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -17356,23 +17356,23 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AS013</t>
+          <t>AS012</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AS013-DISCOUNTED_NTAP</t>
+          <t>AS012-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>140.67</v>
+        <v>460.38</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -17381,23 +17381,23 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AS013</t>
+          <t>AS012</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AS013-OTHER_NTAP</t>
+          <t>AS012-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>57.22</v>
+        <v>1499.98</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -17406,23 +17406,23 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AS013</t>
+          <t>AS012</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AS013-AMIT_GROSS_UP</t>
+          <t>AS012-INTEREST</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>148.89</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -17431,23 +17431,23 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AS013</t>
+          <t>AS012</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AS013-TOTAL_CY_CG</t>
+          <t>AS012-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>355</v>
+        <v>15.96</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -17456,23 +17456,23 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AS013</t>
+          <t>AS012</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AS013-FRANKED_DISTRIBUTION</t>
+          <t>AS012-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FRANKED_DISTRIBUTION</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1463.16</v>
+        <v>150</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -17481,23 +17481,23 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>AS013</t>
+          <t>AS012</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AS013-UNFRANKED_DISTRIBUTION</t>
+          <t>AS012-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>219.48</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -17506,23 +17506,23 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>AS013</t>
+          <t>AS012</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AS013-FOREIGN_SOURCE_INCOME</t>
+          <t>AS013-DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>109.74</v>
+        <v>11.55</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -17538,16 +17538,16 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AS013-INTEREST</t>
+          <t>AS013-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>36.58</v>
+        <v>197.74</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -17563,16 +17563,16 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AS013-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS013-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.97</v>
+        <v>80.42</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -17588,16 +17588,16 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AS013-COSTBASE_INCREASE</t>
+          <t>AS013-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>147.91</v>
+        <v>209.29</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -17613,16 +17613,16 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AS014-DISCOUNTED_NTAP</t>
+          <t>AS013-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>174.24</v>
+        <v>499</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -17631,23 +17631,23 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AS014</t>
+          <t>AS013</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AS014-OTHER_NTAP</t>
+          <t>AS013-FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>67.15000000000001</v>
+        <v>2056.68</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -17656,23 +17656,23 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AS014</t>
+          <t>AS013</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AS014-AMIT_GROSS_UP</t>
+          <t>AS013-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>174.24</v>
+        <v>308.5</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -17681,23 +17681,23 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AS014</t>
+          <t>AS013</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AS014-TOTAL_CY_CG</t>
+          <t>AS013-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>415.63</v>
+        <v>154.25</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -17706,23 +17706,23 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AS014</t>
+          <t>AS013</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AS014-FOREIGN_SOURCE_INCOME</t>
+          <t>AS013-INTEREST</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2371.23</v>
+        <v>51.42</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -17731,23 +17731,23 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AS014</t>
+          <t>AS013</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AS014-INTEREST</t>
+          <t>AS013-FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>126.13</v>
+        <v>881.4299999999999</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -17756,23 +17756,23 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AS014</t>
+          <t>AS013</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AS014-UNFRANKED_DISTRIBUTION</t>
+          <t>AS013-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>25.23</v>
+        <v>15.43</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -17781,23 +17781,23 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>AS014</t>
+          <t>AS013</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AS014-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS013-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>237.12</v>
+        <v>147.91</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -17806,23 +17806,23 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AS014</t>
+          <t>AS013</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AS014-COSTBASE_INCREASE</t>
+          <t>AS014-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>189.54</v>
+        <v>174.24</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -17838,16 +17838,16 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AS015-DISCOUNTED_TAP</t>
+          <t>AS014-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>DISCOUNTED_TAP</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>28.59</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -17856,23 +17856,23 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AS015</t>
+          <t>AS014</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AS015-DISCOUNTED_NTAP</t>
+          <t>AS014-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>335.26</v>
+        <v>174.24</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -17881,23 +17881,23 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AS015</t>
+          <t>AS014</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>AS015-OTHER_NTAP</t>
+          <t>AS014-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>66.03</v>
+        <v>415.63</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -17906,23 +17906,23 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>AS015</t>
+          <t>AS014</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AS015-AMIT_GROSS_UP</t>
+          <t>AS014-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>363.85</v>
+        <v>2371.23</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -17931,23 +17931,23 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AS015</t>
+          <t>AS014</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AS015-TOTAL_CY_CG</t>
+          <t>AS014-INTEREST</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>793.73</v>
+        <v>126.13</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -17956,23 +17956,23 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AS015</t>
+          <t>AS014</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>AS015-FRANKED_DISTRIBUTION</t>
+          <t>AS014-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FRANKED_DISTRIBUTION</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2373.89</v>
+        <v>25.23</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -17981,23 +17981,23 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AS015</t>
+          <t>AS014</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>AS015-UNFRANKED_DISTRIBUTION</t>
+          <t>AS014-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>356.08</v>
+        <v>237.12</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -18006,23 +18006,23 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AS015</t>
+          <t>AS014</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AS015-FOREIGN_SOURCE_INCOME</t>
+          <t>AS014-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>178.04</v>
+        <v>189.54</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -18031,23 +18031,23 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>AS015</t>
+          <t>AS014</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AS015-INTEREST</t>
+          <t>AS015-DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>59.35</v>
+        <v>39.27</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -18063,16 +18063,16 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>AS015-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS015-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>17.8</v>
+        <v>460.39</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -18088,16 +18088,16 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AS015-COSTBASE_DECREASE</t>
+          <t>AS015-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>COSTBASE_DECREASE</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>416.72</v>
+        <v>90.67</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -18113,16 +18113,16 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>AS016-DISCOUNTED_NTAP</t>
+          <t>AS015-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>54.29</v>
+        <v>499.66</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -18131,23 +18131,23 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AS016</t>
+          <t>AS015</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>AS016-OTHER_NTAP</t>
+          <t>AS015-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>19.21</v>
+        <v>1089.99</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -18156,23 +18156,23 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AS016</t>
+          <t>AS015</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>AS016-AMIT_GROSS_UP</t>
+          <t>AS015-FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>54.29</v>
+        <v>3259.87</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -18181,23 +18181,23 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AS016</t>
+          <t>AS015</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>AS016-TOTAL_CY_CG</t>
+          <t>AS015-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>127.79</v>
+        <v>488.98</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -18206,14 +18206,14 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AS016</t>
+          <t>AS015</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>AS016-FOREIGN_SOURCE_INCOME</t>
+          <t>AS015-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -18222,7 +18222,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1874.64</v>
+        <v>244.49</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -18231,14 +18231,14 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AS016</t>
+          <t>AS015</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AS016-INTEREST</t>
+          <t>AS015-INTEREST</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -18247,7 +18247,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>99.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -18256,23 +18256,23 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AS016</t>
+          <t>AS015</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>AS016-UNFRANKED_DISTRIBUTION</t>
+          <t>AS015-FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>19.94</v>
+        <v>1397.09</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -18281,14 +18281,14 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AS016</t>
+          <t>AS015</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AS016-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS015-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -18297,7 +18297,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>187.46</v>
+        <v>24.45</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -18306,14 +18306,14 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AS016</t>
+          <t>AS015</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AS016-COSTBASE_DECREASE</t>
+          <t>AS015-COSTBASE_DECREASE</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -18322,7 +18322,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>89.95999999999999</v>
+        <v>416.72</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AS016</t>
+          <t>AS015</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AS017-DISCOUNTED_TAP</t>
+          <t>AS016-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>DISCOUNTED_TAP</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5.62</v>
+        <v>54.29</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -18356,23 +18356,23 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AS017</t>
+          <t>AS016</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>AS017-DISCOUNTED_NTAP</t>
+          <t>AS016-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>153.54</v>
+        <v>19.21</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -18381,23 +18381,23 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>AS017</t>
+          <t>AS016</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AS017-OTHER_NTAP</t>
+          <t>AS016-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>25.75</v>
+        <v>54.29</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -18406,23 +18406,23 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AS017</t>
+          <t>AS016</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AS017-AMIT_GROSS_UP</t>
+          <t>AS016-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>159.16</v>
+        <v>127.79</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -18431,23 +18431,23 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>AS017</t>
+          <t>AS016</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AS017-TOTAL_CY_CG</t>
+          <t>AS016-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>344.07</v>
+        <v>1874.64</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -18456,23 +18456,23 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>AS017</t>
+          <t>AS016</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>AS017-FRANKED_DISTRIBUTION</t>
+          <t>AS016-INTEREST</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FRANKED_DISTRIBUTION</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2389.9</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -18481,14 +18481,14 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>AS017</t>
+          <t>AS016</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AS017-UNFRANKED_DISTRIBUTION</t>
+          <t>AS016-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>358.48</v>
+        <v>19.94</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -18506,23 +18506,23 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>AS017</t>
+          <t>AS016</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>AS017-FOREIGN_SOURCE_INCOME</t>
+          <t>AS016-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>179.24</v>
+        <v>187.46</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -18531,23 +18531,23 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>AS017</t>
+          <t>AS016</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>AS017-INTEREST</t>
+          <t>AS016-COSTBASE_DECREASE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>COSTBASE_DECREASE</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>59.75</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -18556,23 +18556,23 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>AS017</t>
+          <t>AS016</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>AS017-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS017-DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>17.92</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -18588,16 +18588,16 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>AS017-COSTBASE_INCREASE</t>
+          <t>AS017-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>117.92</v>
+        <v>222.23</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -18613,16 +18613,16 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>AS018-DISCOUNTED_NTAP</t>
+          <t>AS017-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>161.03</v>
+        <v>37.27</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -18631,23 +18631,23 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>AS018</t>
+          <t>AS017</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>AS018-OTHER_NTAP</t>
+          <t>AS017-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>53.01</v>
+        <v>230.37</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -18656,23 +18656,23 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>AS018</t>
+          <t>AS017</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>AS018-AMIT_GROSS_UP</t>
+          <t>AS017-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>161.03</v>
+        <v>498.01</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -18681,23 +18681,23 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>AS018</t>
+          <t>AS017</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>AS018-TOTAL_CY_CG</t>
+          <t>AS017-FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>375.07</v>
+        <v>3459.16</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -18706,23 +18706,23 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>AS018</t>
+          <t>AS017</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>AS018-FOREIGN_SOURCE_INCOME</t>
+          <t>AS017-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>5803.68</v>
+        <v>518.87</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -18731,23 +18731,23 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>AS018</t>
+          <t>AS017</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>AS018-INTEREST</t>
+          <t>AS017-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>308.71</v>
+        <v>259.44</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -18756,23 +18756,23 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AS018</t>
+          <t>AS017</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>AS018-UNFRANKED_DISTRIBUTION</t>
+          <t>AS017-INTEREST</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>61.74</v>
+        <v>86.48</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -18781,23 +18781,23 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AS018</t>
+          <t>AS017</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>AS018-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS017-FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>580.37</v>
+        <v>1482.5</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -18806,23 +18806,23 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>AS018</t>
+          <t>AS017</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>AS018-COSTBASE_INCREASE</t>
+          <t>AS017-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>609.24</v>
+        <v>25.94</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -18831,23 +18831,23 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>AS018</t>
+          <t>AS017</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>AS019-DISCOUNTED_TAP</t>
+          <t>AS017-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>DISCOUNTED_TAP</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>16.63</v>
+        <v>117.92</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -18856,14 +18856,14 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>AS019</t>
+          <t>AS017</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>AS019-DISCOUNTED_NTAP</t>
+          <t>AS018-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -18872,7 +18872,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>338.42</v>
+        <v>161.03</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -18881,14 +18881,14 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>AS019</t>
+          <t>AS018</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>AS019-OTHER_NTAP</t>
+          <t>AS018-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -18897,7 +18897,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>16.82</v>
+        <v>53.01</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -18906,14 +18906,14 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>AS019</t>
+          <t>AS018</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>AS019-AMIT_GROSS_UP</t>
+          <t>AS018-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -18922,7 +18922,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>355.05</v>
+        <v>161.03</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -18931,14 +18931,14 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>AS019</t>
+          <t>AS018</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AS019-TOTAL_CY_CG</t>
+          <t>AS018-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -18947,7 +18947,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>726.92</v>
+        <v>375.07</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -18956,23 +18956,23 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>AS019</t>
+          <t>AS018</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>AS019-FRANKED_DISTRIBUTION</t>
+          <t>AS018-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>FRANKED_DISTRIBUTION</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>2439.03</v>
+        <v>5803.68</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -18981,23 +18981,23 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>AS019</t>
+          <t>AS018</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>AS019-UNFRANKED_DISTRIBUTION</t>
+          <t>AS018-INTEREST</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>365.86</v>
+        <v>308.71</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -19006,23 +19006,23 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>AS019</t>
+          <t>AS018</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>AS019-FOREIGN_SOURCE_INCOME</t>
+          <t>AS018-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>182.93</v>
+        <v>61.74</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -19031,23 +19031,23 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>AS019</t>
+          <t>AS018</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>AS019-INTEREST</t>
+          <t>AS018-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>60.98</v>
+        <v>580.37</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -19056,23 +19056,23 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>AS019</t>
+          <t>AS018</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>AS019-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS018-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>18.29</v>
+        <v>609.24</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -19081,23 +19081,23 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>AS019</t>
+          <t>AS018</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>AS019-COSTBASE_INCREASE</t>
+          <t>AS019-DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>288.25</v>
+        <v>23.04</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -19113,7 +19113,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>AS020-DISCOUNTED_NTAP</t>
+          <t>AS019-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -19122,7 +19122,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>477.98</v>
+        <v>468.86</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -19131,14 +19131,14 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>AS020</t>
+          <t>AS019</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>AS020-OTHER_NTAP</t>
+          <t>AS019-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -19147,7 +19147,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>204.94</v>
+        <v>23.3</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -19156,14 +19156,14 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>AS020</t>
+          <t>AS019</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>AS020-AMIT_GROSS_UP</t>
+          <t>AS019-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -19172,7 +19172,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>477.98</v>
+        <v>491.9</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -19181,14 +19181,14 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>AS020</t>
+          <t>AS019</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>AS020-TOTAL_CY_CG</t>
+          <t>AS019-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -19197,7 +19197,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1160.9</v>
+        <v>1007.1</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -19206,23 +19206,23 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>AS020</t>
+          <t>AS019</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>AS020-FOREIGN_SOURCE_INCOME</t>
+          <t>AS019-FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>7917.34</v>
+        <v>3379.08</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -19231,23 +19231,23 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>AS020</t>
+          <t>AS019</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>AS020-INTEREST</t>
+          <t>AS019-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>421.14</v>
+        <v>506.86</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -19256,23 +19256,23 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>AS020</t>
+          <t>AS019</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AS020-UNFRANKED_DISTRIBUTION</t>
+          <t>AS019-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>84.23</v>
+        <v>253.43</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -19281,23 +19281,23 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>AS020</t>
+          <t>AS019</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>AS020-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS019-INTEREST</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>791.74</v>
+        <v>84.48</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -19306,23 +19306,23 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>AS020</t>
+          <t>AS019</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AS020-COSTBASE_INCREASE</t>
+          <t>AS019-FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>COSTBASE_INCREASE</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>701.45</v>
+        <v>1448.18</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -19331,23 +19331,23 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>AS020</t>
+          <t>AS019</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>AS021-DISCOUNTED_TAP</t>
+          <t>AS019-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DISCOUNTED_TAP</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>16.06</v>
+        <v>25.34</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -19356,23 +19356,23 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>AS021</t>
+          <t>AS019</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>AS021-DISCOUNTED_NTAP</t>
+          <t>AS019-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>261.67</v>
+        <v>288.25</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -19381,23 +19381,23 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>AS021</t>
+          <t>AS019</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>AS021-OTHER_NTAP</t>
+          <t>AS020-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>130.17</v>
+        <v>477.98</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -19406,23 +19406,23 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>AS021</t>
+          <t>AS020</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>AS021-AMIT_GROSS_UP</t>
+          <t>AS020-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>277.73</v>
+        <v>204.94</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -19431,23 +19431,23 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>AS021</t>
+          <t>AS020</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>AS021-TOTAL_CY_CG</t>
+          <t>AS020-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>685.63</v>
+        <v>477.98</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -19456,23 +19456,23 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>AS021</t>
+          <t>AS020</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>AS021-FRANKED_DISTRIBUTION</t>
+          <t>AS020-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>FRANKED_DISTRIBUTION</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>3276.61</v>
+        <v>1160.9</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -19481,23 +19481,23 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AS021</t>
+          <t>AS020</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>AS021-UNFRANKED_DISTRIBUTION</t>
+          <t>AS020-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>491.49</v>
+        <v>7917.34</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -19506,23 +19506,23 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>AS021</t>
+          <t>AS020</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>AS021-FOREIGN_SOURCE_INCOME</t>
+          <t>AS020-INTEREST</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>INTEREST</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>245.75</v>
+        <v>421.14</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -19531,23 +19531,23 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>AS021</t>
+          <t>AS020</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>AS021-INTEREST</t>
+          <t>AS020-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>81.92</v>
+        <v>84.23</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -19556,14 +19556,14 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>AS021</t>
+          <t>AS020</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>AS021-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS020-FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -19572,7 +19572,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>24.58</v>
+        <v>791.74</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -19581,14 +19581,14 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AS021</t>
+          <t>AS020</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>AS021-COSTBASE_INCREASE</t>
+          <t>AS020-COSTBASE_INCREASE</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -19597,7 +19597,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>494.99</v>
+        <v>701.45</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -19606,23 +19606,23 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AS021</t>
+          <t>AS020</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>AS022-DISCOUNTED_NTAP</t>
+          <t>AS021-DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>DISCOUNTED_NTAP</t>
+          <t>DISCOUNTED_TAP</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>504.26</v>
+        <v>22.79</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -19631,23 +19631,23 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>AS022</t>
+          <t>AS021</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>AS022-OTHER_NTAP</t>
+          <t>AS021-DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>OTHER_NTAP</t>
+          <t>DISCOUNTED_NTAP</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>209.25</v>
+        <v>371.27</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -19656,23 +19656,23 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>AS022</t>
+          <t>AS021</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>AS022-AMIT_GROSS_UP</t>
+          <t>AS021-OTHER_NTAP</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>AMIT_GROSS_UP</t>
+          <t>OTHER_NTAP</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>504.26</v>
+        <v>184.69</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -19681,23 +19681,23 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>AS022</t>
+          <t>AS021</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>AS022-TOTAL_CY_CG</t>
+          <t>AS021-AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>TOTAL_CY_CG</t>
+          <t>AMIT_GROSS_UP</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1217.77</v>
+        <v>394.06</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -19706,23 +19706,23 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>AS022</t>
+          <t>AS021</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>AS022-FOREIGN_SOURCE_INCOME</t>
+          <t>AS021-TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>TOTAL_CY_CG</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>3699.43</v>
+        <v>972.8099999999999</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -19731,23 +19731,23 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>AS022</t>
+          <t>AS021</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>AS022-INTEREST</t>
+          <t>AS021-FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>FRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>196.78</v>
+        <v>4649.06</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -19756,14 +19756,14 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>AS022</t>
+          <t>AS021</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>AS022-UNFRANKED_DISTRIBUTION</t>
+          <t>AS021-UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -19772,7 +19772,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>39.36</v>
+        <v>697.36</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -19781,23 +19781,23 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>AS022</t>
+          <t>AS021</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>AS022-FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>AS021-FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>369.94</v>
+        <v>348.68</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -19806,30 +19806,330 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>AS022</t>
+          <t>AS021</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
+          <t>AS021-INTEREST</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>INTEREST</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>116.23</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>AS021</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>AS021-FRANKING_CREDIT</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>FRANKING_CREDIT</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1992.45</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>AS021</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>AS021-FOREIGN_INCOME_TAX_OFFSET</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>AS021</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>AS021-COSTBASE_INCREASE</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>COSTBASE_INCREASE</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>494.99</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>AS021</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>AS022-DISCOUNTED_NTAP</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>DISCOUNTED_NTAP</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>504.26</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>AS022</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>AS022-OTHER_NTAP</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>OTHER_NTAP</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>209.25</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>AS022</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>AS022-AMIT_GROSS_UP</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>AMIT_GROSS_UP</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>504.26</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>AS022</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>AS022-TOTAL_CY_CG</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>TOTAL_CY_CG</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>1217.77</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>AS022</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>AS022-FOREIGN_SOURCE_INCOME</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>FOREIGN_SOURCE_INCOME</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>3699.43</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>AS022</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>AS022-INTEREST</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>INTEREST</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>196.78</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>AS022</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>AS022-UNFRANKED_DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>UNFRANKED_DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>AS022</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>AS022-FOREIGN_INCOME_TAX_OFFSET</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>369.94</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>AS022</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
           <t>AS022-COSTBASE_INCREASE</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C231" t="inlineStr">
         <is>
           <t>COSTBASE_INCREASE</t>
         </is>
       </c>
-      <c r="D219" t="n">
+      <c r="D231" t="n">
         <v>109.68</v>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>AUD</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
         <is>
           <t>AS022</t>
         </is>
@@ -19837,10 +20137,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C719" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick a value for component from the list." type="list">
-      <formula1>'ValueAssistance'!$K$2:$K$27</formula1>
+    <dataValidation sqref="C2:C731" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick a value for component from the list." type="list">
+      <formula1>'ValueAssistance'!$K$2:$K$28</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E719" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick a value for amount_currency from the list." type="list">
+    <dataValidation sqref="E2:E731" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick a value for amount_currency from the list." type="list">
       <formula1>'ValueAssistance'!$B$2:$B$308</formula1>
     </dataValidation>
   </dataValidations>
@@ -20592,7 +20892,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>UNFRANKED_DISTRIBUTION</t>
+          <t>FRANKING_CREDIT</t>
         </is>
       </c>
     </row>
@@ -20604,7 +20904,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>INTEREST</t>
+          <t>UNFRANKED_DISTRIBUTION</t>
         </is>
       </c>
     </row>
@@ -20616,7 +20916,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>OTHER_INCOME</t>
+          <t>INTEREST</t>
         </is>
       </c>
     </row>
@@ -20628,7 +20928,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>FOREIGN_SOURCE_INCOME</t>
+          <t>OTHER_INCOME</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20940,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>FOREIGN_INCOME_TAX_OFFSET</t>
+          <t>FOREIGN_SOURCE_INCOME</t>
         </is>
       </c>
     </row>
@@ -20652,7 +20952,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>NON_ASSESSABLE_NON_EXEMPT</t>
+          <t>FOREIGN_INCOME_TAX_OFFSET</t>
         </is>
       </c>
     </row>
@@ -20664,7 +20964,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>WITHHOLDING_CREDIT</t>
+          <t>NON_ASSESSABLE_NON_EXEMPT</t>
         </is>
       </c>
     </row>
@@ -20676,7 +20976,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>WITHHOLDING_DEDUCTED</t>
+          <t>WITHHOLDING_CREDIT</t>
         </is>
       </c>
     </row>
@@ -20684,6 +20984,11 @@
       <c r="B28" t="inlineStr">
         <is>
           <t>BYN</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>WITHHOLDING_DEDUCTED</t>
         </is>
       </c>
     </row>
